--- a/data/Test.xlsx
+++ b/data/Test.xlsx
@@ -448,70 +448,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>map&lt;string,string&gt;</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>map&lt;string,string&gt;</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 key; uint32 value }</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="F5" t="inlineStr">
         <is>
